--- a/策划/数值文档/monster_c.xlsx
+++ b/策划/数值文档/monster_c.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="122">
   <si>
     <t>id</t>
   </si>
@@ -118,6 +118,12 @@
     <t>treasure_class</t>
   </si>
   <si>
+    <t>treasure_class_champ</t>
+  </si>
+  <si>
+    <t>treasure_class_unique</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
@@ -229,7 +235,13 @@
     <t>飞行（官方 flying）</t>
   </si>
   <si>
-    <t>掉落表（官方 TreasureClass1，指向 treasureclass_c）</t>
+    <t>掉落表（官方 TreasureClass1 = 普通怪槽位，指向 treasureclass_c）</t>
+  </si>
+  <si>
+    <t>冠军怪掉落表（官方 TreasureClass2）</t>
+  </si>
+  <si>
+    <t>唯一（精英）怪掉落表（官方 TreasureClass3）</t>
   </si>
   <si>
     <t>堕落者</t>
@@ -247,6 +259,12 @@
     <t>Act 1 H2H A</t>
   </si>
   <si>
+    <t>Act 1 Champ A</t>
+  </si>
+  <si>
+    <t>Act 1 Unique A</t>
+  </si>
+  <si>
     <t>堕落萨满</t>
   </si>
   <si>
@@ -320,6 +338,12 @@
   </si>
   <si>
     <t>Act 1 Cast B</t>
+  </si>
+  <si>
+    <t>Act 1 Champ B</t>
+  </si>
+  <si>
+    <t>Act 1 Unique B</t>
   </si>
   <si>
     <t>巨兽</t>
@@ -764,317 +788,341 @@
       <c r="AH1" t="s">
         <v>33</v>
       </c>
+      <c r="AI1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AJ1" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="I2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="L2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="M2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="N2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="O2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="P2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Q2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="R2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="S2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="T2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="U2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="V2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="W2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="X2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Y2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Z2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AA2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AB2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="AC2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AD2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AE2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AF2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AG2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AH2" t="s">
-        <v>35</v>
+        <v>37</v>
+      </c>
+      <c r="AI2" t="s">
+        <v>37</v>
+      </c>
+      <c r="AJ2" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="H3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="J3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="K3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="L3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="N3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="O3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="P3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="Q3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="R3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="S3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="T3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="U3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="V3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="W3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="X3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="Y3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="Z3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="AA3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="AB3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="AC3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="AD3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="AE3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="AF3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="AG3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="AH3" t="s">
-        <v>37</v>
+        <v>39</v>
+      </c>
+      <c r="AI3" t="s">
+        <v>39</v>
+      </c>
+      <c r="AJ3" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G4" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="H4" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="I4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="J4" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="K4" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="L4" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="M4" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="N4" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="O4" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="P4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="Q4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="R4" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="S4" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="T4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="U4" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="V4" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="W4" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="X4" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="Y4" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="Z4" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="AA4" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="AB4" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="AC4" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="AD4" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="AE4" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="AF4" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="AG4" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="AH4" t="s">
-        <v>71</v>
+        <v>73</v>
+      </c>
+      <c r="AI4" t="s">
+        <v>74</v>
+      </c>
+      <c r="AJ4" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="5">
@@ -1082,16 +1130,16 @@
         <v>1</v>
       </c>
       <c r="B5" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C5" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="D5" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="E5" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="F5">
         <v>1</v>
@@ -1133,7 +1181,7 @@
         <v>18</v>
       </c>
       <c r="S5" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="T5">
         <v>5</v>
@@ -1160,7 +1208,7 @@
         <v>0</v>
       </c>
       <c r="AB5" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AC5">
         <v>1</v>
@@ -1178,7 +1226,13 @@
         <v>0</v>
       </c>
       <c r="AH5" t="s">
-        <v>76</v>
+        <v>80</v>
+      </c>
+      <c r="AI5" t="s">
+        <v>81</v>
+      </c>
+      <c r="AJ5" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="6">
@@ -1186,16 +1240,16 @@
         <v>2</v>
       </c>
       <c r="B6" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="C6" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="D6" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="E6" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="F6">
         <v>1</v>
@@ -1237,7 +1291,7 @@
         <v>24</v>
       </c>
       <c r="S6" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="T6">
         <v>4</v>
@@ -1264,7 +1318,7 @@
         <v>0</v>
       </c>
       <c r="AB6" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="AC6">
         <v>1</v>
@@ -1282,7 +1336,13 @@
         <v>0</v>
       </c>
       <c r="AH6" t="s">
+        <v>87</v>
+      </c>
+      <c r="AI6" t="s">
         <v>81</v>
+      </c>
+      <c r="AJ6" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="7">
@@ -1290,16 +1350,16 @@
         <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="C7" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="D7" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="E7" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="F7">
         <v>1</v>
@@ -1341,7 +1401,7 @@
         <v>21</v>
       </c>
       <c r="S7" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="T7">
         <v>3</v>
@@ -1368,7 +1428,7 @@
         <v>0</v>
       </c>
       <c r="AB7" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="AC7">
         <v>1</v>
@@ -1386,7 +1446,13 @@
         <v>0</v>
       </c>
       <c r="AH7" t="s">
-        <v>86</v>
+        <v>92</v>
+      </c>
+      <c r="AI7" t="s">
+        <v>81</v>
+      </c>
+      <c r="AJ7" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="8">
@@ -1394,16 +1460,16 @@
         <v>4</v>
       </c>
       <c r="B8" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="C8" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="D8" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="E8" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="F8">
         <v>1</v>
@@ -1445,7 +1511,7 @@
         <v>33</v>
       </c>
       <c r="S8" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="T8">
         <v>1</v>
@@ -1472,7 +1538,7 @@
         <v>50</v>
       </c>
       <c r="AB8" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="AC8">
         <v>1</v>
@@ -1490,7 +1556,13 @@
         <v>0</v>
       </c>
       <c r="AH8" t="s">
-        <v>76</v>
+        <v>80</v>
+      </c>
+      <c r="AI8" t="s">
+        <v>81</v>
+      </c>
+      <c r="AJ8" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="9">
@@ -1498,16 +1570,16 @@
         <v>5</v>
       </c>
       <c r="B9" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="C9" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="D9" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="E9" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="F9">
         <v>1</v>
@@ -1549,7 +1621,7 @@
         <v>23</v>
       </c>
       <c r="S9" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="T9">
         <v>5</v>
@@ -1576,7 +1648,7 @@
         <v>0</v>
       </c>
       <c r="AB9" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="AC9">
         <v>1</v>
@@ -1594,7 +1666,13 @@
         <v>0</v>
       </c>
       <c r="AH9" t="s">
-        <v>76</v>
+        <v>80</v>
+      </c>
+      <c r="AI9" t="s">
+        <v>81</v>
+      </c>
+      <c r="AJ9" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="10">
@@ -1602,16 +1680,16 @@
         <v>6</v>
       </c>
       <c r="B10" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="C10" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="D10" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="E10" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="F10">
         <v>1</v>
@@ -1653,7 +1731,7 @@
         <v>11</v>
       </c>
       <c r="S10" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="T10">
         <v>4</v>
@@ -1680,7 +1758,7 @@
         <v>0</v>
       </c>
       <c r="AB10" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="AC10">
         <v>1</v>
@@ -1698,7 +1776,13 @@
         <v>1</v>
       </c>
       <c r="AH10" t="s">
-        <v>101</v>
+        <v>107</v>
+      </c>
+      <c r="AI10" t="s">
+        <v>108</v>
+      </c>
+      <c r="AJ10" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="11">
@@ -1706,16 +1790,16 @@
         <v>7</v>
       </c>
       <c r="B11" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="C11" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="D11" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="E11" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="F11">
         <v>1</v>
@@ -1757,7 +1841,7 @@
         <v>36</v>
       </c>
       <c r="S11" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="T11">
         <v>3</v>
@@ -1784,7 +1868,7 @@
         <v>0</v>
       </c>
       <c r="AB11" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="AC11">
         <v>1</v>
@@ -1802,7 +1886,13 @@
         <v>0</v>
       </c>
       <c r="AH11" t="s">
-        <v>76</v>
+        <v>80</v>
+      </c>
+      <c r="AI11" t="s">
+        <v>81</v>
+      </c>
+      <c r="AJ11" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="12">
@@ -1810,16 +1900,16 @@
         <v>8</v>
       </c>
       <c r="B12" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="C12" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="D12" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="E12" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="F12">
         <v>1</v>
@@ -1861,7 +1951,7 @@
         <v>27</v>
       </c>
       <c r="S12" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="T12">
         <v>5</v>
@@ -1888,7 +1978,7 @@
         <v>50</v>
       </c>
       <c r="AB12" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="AC12">
         <v>1</v>
@@ -1906,7 +1996,13 @@
         <v>1</v>
       </c>
       <c r="AH12" t="s">
-        <v>113</v>
+        <v>121</v>
+      </c>
+      <c r="AI12" t="s">
+        <v>108</v>
+      </c>
+      <c r="AJ12" t="s">
+        <v>109</v>
       </c>
     </row>
   </sheetData>
